--- a/artfynd/A 22929-2025 artfynd.xlsx
+++ b/artfynd/A 22929-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109276038</v>
+        <v>109276029</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541809.0228056316</v>
+        <v>541977</v>
       </c>
       <c r="R2" t="n">
-        <v>6968768.568282198</v>
+        <v>6968533</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109276033</v>
+        <v>109276036</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541901.0408093991</v>
+        <v>541845</v>
       </c>
       <c r="R3" t="n">
-        <v>6968619.905617887</v>
+        <v>6968747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109276030</v>
+        <v>109838476</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor Abborselberget, Jmt</t>
+          <t>Storabborselsberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541977.1827809595</v>
+        <v>541983</v>
       </c>
       <c r="R4" t="n">
-        <v>6968532.709836086</v>
+        <v>6968416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109276036</v>
+        <v>109913975</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541845.4354613087</v>
+        <v>542026</v>
       </c>
       <c r="R5" t="n">
-        <v>6968747.105845867</v>
+        <v>6968339</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109276022</v>
+        <v>109276017</v>
       </c>
       <c r="B6" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542120.4176459897</v>
+        <v>541884</v>
       </c>
       <c r="R6" t="n">
-        <v>6968422.617943348</v>
+        <v>6968666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109276028</v>
+        <v>109276021</v>
       </c>
       <c r="B7" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542020.1551533042</v>
+        <v>542024</v>
       </c>
       <c r="R7" t="n">
-        <v>6968499.453627682</v>
+        <v>6968450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109276027</v>
+        <v>109276034</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542073.6431983345</v>
+        <v>541901</v>
       </c>
       <c r="R8" t="n">
-        <v>6968466.789393404</v>
+        <v>6968620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109276032</v>
+        <v>109913972</v>
       </c>
       <c r="B9" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541870.3985244536</v>
+        <v>542005</v>
       </c>
       <c r="R9" t="n">
-        <v>6968583.424245842</v>
+        <v>6968252</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109276031</v>
+        <v>109276028</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541980.4853132684</v>
+        <v>542020</v>
       </c>
       <c r="R10" t="n">
-        <v>6968560.619501093</v>
+        <v>6968499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109276017</v>
+        <v>109913970</v>
       </c>
       <c r="B11" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541884.4483550336</v>
+        <v>541906</v>
       </c>
       <c r="R11" t="n">
-        <v>6968665.376471159</v>
+        <v>6968140</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109276024</v>
+        <v>109276020</v>
       </c>
       <c r="B12" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>5260</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542119.6372317184</v>
+        <v>541871</v>
       </c>
       <c r="R12" t="n">
-        <v>6968483.369752945</v>
+        <v>6968407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,50 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109276034</v>
+        <v>109838473</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5260</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stor Abborselberget, Jmt</t>
+          <t>Storabborselsberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541901.0408093991</v>
+        <v>541873</v>
       </c>
       <c r="R13" t="n">
-        <v>6968619.905617887</v>
+        <v>6968405</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,49 +1827,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109276021</v>
+        <v>109913971</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542023.9893316111</v>
+        <v>542005</v>
       </c>
       <c r="R14" t="n">
-        <v>6968450.162699901</v>
+        <v>6968252</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,22 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109276037</v>
+        <v>109276039</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor Abborselberget, Jmt</t>
+          <t>Stor Abborrselberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541845.4354613087</v>
+        <v>541809</v>
       </c>
       <c r="R15" t="n">
-        <v>6968747.105845867</v>
+        <v>6968769</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109276023</v>
+        <v>109913965</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542119.6372317184</v>
+        <v>541954</v>
       </c>
       <c r="R16" t="n">
-        <v>6968483.369752945</v>
+        <v>6968329</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,22 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,12 +2133,7 @@
         <v>109276026</v>
       </c>
       <c r="B17" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542088.3745228138</v>
+        <v>542088</v>
       </c>
       <c r="R17" t="n">
-        <v>6968495.303272387</v>
+        <v>6968495</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109276039</v>
+        <v>109276032</v>
       </c>
       <c r="B18" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,34 +2238,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor Abborrselberget, Jmt</t>
+          <t>Stor Abborselberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541809.0228056316</v>
+        <v>541870</v>
       </c>
       <c r="R18" t="n">
-        <v>6968768.568282198</v>
+        <v>6968583</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2295,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109276029</v>
+        <v>109838474</v>
       </c>
       <c r="B19" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,34 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor Abborselberget, Jmt</t>
+          <t>Storabborselsberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541977.1827809595</v>
+        <v>541907</v>
       </c>
       <c r="R19" t="n">
-        <v>6968532.709836086</v>
+        <v>6968402</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,19 +2392,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,49 +2409,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109914132</v>
+        <v>109913962</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542051.6685053414</v>
+        <v>541929</v>
       </c>
       <c r="R20" t="n">
-        <v>6968396.608124768</v>
+        <v>6968274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2764,19 +2489,9 @@
           <t>2023-06-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,12 +2521,7 @@
         <v>109913966</v>
       </c>
       <c r="B21" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541842.6758470818</v>
+        <v>541842</v>
       </c>
       <c r="R21" t="n">
-        <v>6968318.094364192</v>
+        <v>6968318</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2876,19 +2586,9 @@
           <t>2023-06-07</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109914120</v>
+        <v>109276023</v>
       </c>
       <c r="B22" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541954.6201717162</v>
+        <v>542119</v>
       </c>
       <c r="R22" t="n">
-        <v>6968329.575970244</v>
+        <v>6968484</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,22 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109913975</v>
+        <v>109276033</v>
       </c>
       <c r="B23" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542025.4061129162</v>
+        <v>541901</v>
       </c>
       <c r="R23" t="n">
-        <v>6968339.619870672</v>
+        <v>6968620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,22 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109914124</v>
+        <v>109276037</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541862.7922765984</v>
+        <v>541845</v>
       </c>
       <c r="R24" t="n">
-        <v>6968247.534961017</v>
+        <v>6968747</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,22 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,50 +2906,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109914129</v>
+        <v>109838477</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor Abborselberget, Jmt</t>
+          <t>Storabborselsberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542027.0938095057</v>
+        <v>541938</v>
       </c>
       <c r="R25" t="n">
-        <v>6968279.333941342</v>
+        <v>6968473</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,22 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,27 +2991,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109913967</v>
+        <v>109913963</v>
       </c>
       <c r="B26" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541842.6758470818</v>
+        <v>541931</v>
       </c>
       <c r="R26" t="n">
-        <v>6968318.094364192</v>
+        <v>6968293</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3436,19 +3071,9 @@
           <t>2023-06-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109913971</v>
+        <v>109276027</v>
       </c>
       <c r="B27" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542005.4816511185</v>
+        <v>542074</v>
       </c>
       <c r="R27" t="n">
-        <v>6968252.101008557</v>
+        <v>6968467</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3545,22 +3165,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109913970</v>
+        <v>109276022</v>
       </c>
       <c r="B28" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541905.8037954222</v>
+        <v>542120</v>
       </c>
       <c r="R28" t="n">
-        <v>6968139.801178516</v>
+        <v>6968423</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3657,22 +3262,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,37 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109914128</v>
+        <v>109276024</v>
       </c>
       <c r="B29" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3739,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542005.4816511185</v>
+        <v>542119</v>
       </c>
       <c r="R29" t="n">
-        <v>6968252.101008557</v>
+        <v>6968484</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,22 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,37 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109913963</v>
+        <v>109276030</v>
       </c>
       <c r="B30" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3851,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541930.8373701186</v>
+        <v>541977</v>
       </c>
       <c r="R30" t="n">
-        <v>6968293.178646906</v>
+        <v>6968533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,22 +3456,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,37 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109913962</v>
+        <v>109276031</v>
       </c>
       <c r="B31" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3963,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541929.2470791503</v>
+        <v>541981</v>
       </c>
       <c r="R31" t="n">
-        <v>6968274.426287684</v>
+        <v>6968561</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3993,22 +3553,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,37 +3585,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109914133</v>
+        <v>109913974</v>
       </c>
       <c r="B32" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542059.3393419586</v>
+        <v>542027</v>
       </c>
       <c r="R32" t="n">
-        <v>6968404.930043043</v>
+        <v>6968280</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4108,19 +3653,9 @@
           <t>2023-06-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,6 +3679,491 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>109913976</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stor Abborselberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>542051</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6968397</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>109276038</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stor Abborselberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>541809</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6968769</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>109838475</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storabborselsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>541964</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6968410</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>109913967</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stor Abborselberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>541842</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6968318</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>109913977</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stor Abborselberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>542060</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6968405</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22929-2025 artfynd.xlsx
+++ b/artfynd/A 22929-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276029</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276036</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913975</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276017</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276021</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276034</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913972</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276028</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913970</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276020</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838473</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913971</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276039</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913965</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276032</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838474</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913962</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913966</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276023</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276033</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276037</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838477</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913963</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276027</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276022</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276024</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276030</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276031</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913974</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913976</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109276038</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838475</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913967</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,8 +4344,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>